--- a/examples/07_validation_errors/broken_config.xlsx
+++ b/examples/07_validation_errors/broken_config.xlsx
@@ -171,39 +171,49 @@
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
         <t>target (optional)
-Database engine to push into.
+Which database to push into.
+  'sqlite'  → a local file (good for testing and small datasets)
+  'postgres' → a PostgreSQL server (production use)
+Example: use 'sqlite' while developing, then switch to 'postgres' for production.
 Allowed: sqlite | postgres (default sqlite)
-Example: sqlite</t>
+Example: postgres</t>
       </text>
     </comment>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>database (optional)
-SQLite: the file path. PostgreSQL: the database NAME.
-Allowed: any path for sqlite; a plain name for postgres. Blank = take it from the command line / PGDATABASE
-Example: loaded.db</t>
+SQLite: the file path (e.g. 'loaded.db' creates a file in the working directory).
+PostgreSQL: the database NAME (e.g. 'excel_parser').
+Leave blank to take it from the command line (--database) or the PGDATABASE environment variable.
+Allowed: any path for sqlite; a plain name for postgres
+Example: excel_parser</t>
       </text>
     </comment>
     <comment ref="A4" authorId="0" shapeId="0">
       <text>
         <t>db_schema (optional)
-PostgreSQL schema to load into; created if it does not exist.
-Allowed: plain name; blank = public. Ignored by SQLite, which has no schemas
+PostgreSQL schema to load into. Created automatically if it does not exist.
+Example: 'staging' puts all tables under the 'staging' schema. Blank = the 'public' schema. Ignored by SQLite (no schemas).
+Allowed: plain name; blank = public. Ignored by SQLite
 Example: staging</t>
       </text>
     </comment>
     <comment ref="A5" authorId="0" shapeId="0">
       <text>
         <t>table_prefix (optional)
-Put in front of every generated table name, e.g. stg_ turns sales into stg_sales.
-Allowed: plain name fragment, letters/digits/underscore; blank = no prefix (default)
+A prefix added to every table name.
+Example: if table_prefix='stg_' and table_name='orders', the physical table is 'stg_orders'. Useful for separating staging from production tables in the same schema.
+Blank = no prefix (default).
+Allowed: plain name fragment; blank = no prefix
 Example: (blank)</t>
       </text>
     </comment>
     <comment ref="A6" authorId="0" shapeId="0">
       <text>
         <t>id_type (optional)
-How every primary key and the file_id are generated: a database counter (1, 2, 3...) or a UUID generated for each row.
+How primary keys and file_id are generated.
+  'integer' → auto-incrementing numbers (1, 2, 3...) — simpler, default.
+  'uuid'    → random UUIDs per row — use when merging data from multiple sources where integer IDs would collide.
 Allowed: integer | uuid (default integer)
 Example: integer</t>
       </text>
@@ -221,31 +231,37 @@
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>table_name (required)
-Logical table name for this block. The table created is &lt;table_prefix&gt;&lt;table_name&gt;.
+The database table name for this block. The physical table becomes &lt;table_prefix&gt;&lt;table_name&gt;.
+Example: if your source has an 'Orders' tab, you might name it 'orders'. Two blocks on the same sheet need different names — e.g. 'card_payments' and 'cash_payments' for two sections on a 'Payments' tab.
 Allowed: lowercase letters, digits, underscore; unique in the workbook; max 63 chars
-Example: sales</t>
+Example: orders</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>sheet_name (required)
-Worksheet tab in the SOURCE workbook that this block sits on.
-Allowed: must match the tab name character for character (Excel truncates long tab names)
-Example: Sales</t>
+The exact tab name in the SOURCE workbook. Must match character for character — copy-paste it from the tab to avoid typos.
+Example: if the tab is called 'Order Level', type exactly 'Order Level'. Excel truncates long tab names (e.g. 'Growth Investments and Other De'), so copy the truncated name.
+Allowed: exact tab name from the source file
+Example: Order Level</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>layout (required)
-Shape of the block. Documentation for the reader - both are read cell by cell.
-Allowed: table = header row + data rows | key_value = label column + value column
+Describes the shape of the data block:
+  'table' = a header row (e.g. row 1) followed by data rows below it.
+  'key_value' = labels in one column, values in the next (like a settings block).
+Example: a list of orders with columns Date, Customer, Amount → 'table'. A summary block with 'Total Orders: 42' on one row → 'key_value'.
+Allowed: table | key_value
 Example: table</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>header_row (optional)
-Row that holds the printed headers. Never read as data; kept for the audit table.
+The row number that contains column headers (e.g. 'Date', 'Customer', 'Amount'). Not read as data — only recorded in the audit log.
+Example: if row 1 has headers and data starts at row 2, set header_row=1. Leave blank for key_value layout.
 Allowed: whole number, 1-based as shown in Excel; blank for key_value
 Example: 1</t>
       </text>
@@ -253,7 +269,8 @@
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>data_start_row (required)
-First row of real data.
+The FIRST row of actual data (not the header, not a title row). Look at the row numbers in Excel.
+Example: if row 1 is headers and data starts at row 2, set data_start_row=2. If there is a title on rows 1–3, headers on row 4, and data from row 5, set data_start_row=5.
 Allowed: whole number, must be below the header/title row
 Example: 2</t>
       </text>
@@ -261,7 +278,9 @@
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>data_end_row (optional)
-Last row of real data. Set it to fence off a totals row, notes, or a second block further down the sheet.
+The LAST row of data. Set this when there are totals, notes, or another data block below.
+Example: data in rows 2–50, then a 'Grand Total' on row 51 → set data_end_row=50. If another block starts at row 55, fence this one off at row 50.
+Leave blank to read to the last non-empty row in the sheet.
 Allowed: whole number &gt;= data_start_row; blank = read to the last used row
 Example: (blank)</t>
       </text>
@@ -269,15 +288,16 @@
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>active (required)
-Switch the block off without deleting the rows.
-Allowed: Y = generate the table and load it | N = ignore completely
+Y = this block is processed (table created, data loaded).
+N = completely skipped — use this to park a block you do not want right now without deleting the row.
+Allowed: Y | N
 Example: Y</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
         <t>notes (optional)
-Free text; copied into the generated SQL as a comment.
+Free text for your own use. Copied into the generated SQL as a comment.
 Allowed: any text
 Example: invoice lines, one row per invoice</t>
       </text>
@@ -290,45 +310,57 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>excel parser</author>
-    <author>Excel Parser</author>
   </authors>
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <t>table_name (required)
-Which sheet_config block this column belongs to.
+Which block (from sheet_config) this column belongs to.
+Example: if you defined a block called 'orders' in sheet_config, every column row for that block has table_name='orders'.
 Allowed: must match a table_name on sheet_config
-Example: sales</t>
+Example: orders</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>source_ref (required)
-Which Excel column of that block to read. Read by POSITION - re-check it whenever the supplier inserts a column.
-Allowed: col:&lt;letter&gt;, e.g. col:A, col:AM. No row numbers, no ranges, no formulas
+Which Excel column letter to read FROM the source file. The parser reads by column position, NOT by header text.
+Example: if 'Order ID' is in column A → 'col:A'. If 'Amount' is in column D → 'col:D'. Wide sheets: column 30 = 'col:AD'.
+IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all source_ref values when that happens.
+Allowed: col:&lt;letter&gt; (e.g. col:A, col:B, col:AM). No row numbers, no ranges
 Example: col:A</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>source_header (optional)
-The header text as printed in the source file.
-Allowed: any text; documentation only, a renamed header does not break the load
+The header text as printed in the source file — purely for documentation. The parser never matches by header text; it always uses source_ref.
+Example: if column A has header 'Invoice No', put 'Invoice No' here. This shows up in the ER diagram and preview tooltips. If the supplier renames the header, the load still works — only source_ref matters.
+Allowed: any text; documentation only
 Example: Invoice No</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>column_name (required)
-Database column name to create.
-Allowed: lowercase letters/digits/underscore, unique within the table, max 63 chars; not file_id, sheet_name, source_row_num or &lt;table_name&gt;_id
+The database column name to create. Must be unique within the table.
+Example: 'Invoice No' → 'invoice_no', 'Order Date' → 'order_date'.
+Reserved names (added automatically): file_id, sheet_name, source_row_num, &lt;table_name&gt;_id — do not use these.
+Allowed: lowercase letters/digits/underscore, unique within the table, max 63 chars
 Example: invoice_no</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>data_type (required)
-How the cell is converted. Pick it from the messiest value in the column, not the first one.
+How the cell value is converted. Choose the type based on the MESSIEST value in the column, not just the first row.
+  text     → keeps the text, trims whitespace. Use for names, IDs, mixed content.
+  numeric  → extracts numbers: '₹1,234.50' → 1234.5, '18%' → 18.0
+  integer  → like numeric but truncated: '42.0' → 42
+  date     → converts to YYYY-MM-DD: '02-Aug-2026' → '2026-08-02'
+  timestamp → date + time: '2026-08-02 19:45'
+  boolean  → yes/true/1 → 1, no/false/0 → 0
+If ANY cell can hold '-', 'NA', or a note, use 'text' to avoid NULLs.
 Allowed: text | numeric | integer | date | timestamp | boolean
 Example: text</t>
       </text>
@@ -336,57 +368,32 @@
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>nullable (required)
-May the cell be empty?
-Allowed: Y = allowed | N = NOT NULL, and a row with it empty is rejected and reported
-Example: N</t>
+Can this column be empty in the source?
+  Y = empty cells are stored as NULL (most columns should use this).
+  N = NOT NULL — any row where this cell is empty is rejected and reported, not loaded.
+Example: 'order_id' should be N (every order must have an ID). 'discount' should be Y (not all orders have a discount).
+When in doubt, use Y — it is safer and you can tighten later.
+Allowed: Y | N
+Example: Y</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <t>is_key (required)
-Create a plain index on this column (for lookups). NOT a primary key and it does not deduplicate.
+Creates a non-unique INDEX on this column for faster lookups. This is NOT a primary key and does NOT deduplicate rows.
+Example: set Y on 'order_id' or 'invoice_no' — columns you will filter or join on. Set N on 'amount', 'description', etc.
 Allowed: Y | N
-Example: Y</t>
+Example: N</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>transform (optional)
-Intent of the cleaning. Documentation - the actual cleaning comes from data_type.
-Allowed: trim | money | percent | date | blank
-Example: trim</t>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
-      <text>
         <t>column_order (required)
-Position of the column in the created table.
-Allowed: whole number; gaps are fine, duplicates make the order arbitrary
+Controls the position of this column in the created table. Number them 1, 2, 3... in the order you want.
+Example: invoice_no=1, invoice_date=2, customer=3, amount=4.
+Gaps are fine (1, 5, 10); duplicates make the order arbitrary.
+Allowed: whole number
 Example: 1</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="1" shapeId="0">
-      <text>
-        <t>references (optional)
-Declares a foreign-key relationship to another table's column.
-Drawn as a dashed line in the ER diagram.
-Allowed: table_name.column_name (e.g. orders.order_id)
-Blank = no relationship declared.
-Does NOT create a database constraint — it is for
-documentation and the diagram only.</t>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="1" shapeId="0">
-      <text>
-        <t>null_default (optional)
-What value to store when the cell is empty or NULL.
-Allowed:
-  blank or "null" = store NULL (default)
-  0 = store zero (for numeric/integer)
-  any text = store that string (for text)
-  0 / 1 / true / false = store that boolean
-Applied after type casting, so a cell with "-" or "NA"
-that casts to NULL will also get this default value.</t>
       </text>
     </comment>
   </commentList>
@@ -715,7 +722,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>sqlite</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -732,7 +739,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>excel_parser</t>
+          <t>broken.db</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -747,11 +754,6 @@
           <t>db_schema</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>broken</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>postgres schema, created if absent; blank = public</t>
@@ -764,7 +766,6 @@
           <t>table_prefix</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>prefix put in front of every table name; blank = none</t>
@@ -966,7 +967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -976,8 +977,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1018,22 +1018,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>transform</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
           <t>column_order</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>references</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>null_default</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1058,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1118,12 +1098,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1163,7 +1138,7 @@
           <t>N</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="H4" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1203,12 +1178,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="H5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1248,12 +1218,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>trim</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
+      <c r="H6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1326,7 +1291,10 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Database engine to push into.</t>
+          <t>Which database to push into.
+  'sqlite'  → a local file (good for testing and small datasets)
+  'postgres' → a PostgreSQL server (production use)
+Example: use 'sqlite' while developing, then switch to 'postgres' for production.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1336,7 +1304,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1321,19 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>SQLite: the file path. PostgreSQL: the database NAME.</t>
+          <t>SQLite: the file path (e.g. 'loaded.db' creates a file in the working directory).
+PostgreSQL: the database NAME (e.g. 'excel_parser').
+Leave blank to take it from the command line (--database) or the PGDATABASE environment variable.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>any path for sqlite; a plain name for postgres. Blank = take it from the command line / PGDATABASE</t>
+          <t>any path for sqlite; a plain name for postgres</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>loaded.db</t>
+          <t>excel_parser</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1350,13 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>PostgreSQL schema to load into; created if it does not exist.</t>
+          <t>PostgreSQL schema to load into. Created automatically if it does not exist.
+Example: 'staging' puts all tables under the 'staging' schema. Blank = the 'public' schema. Ignored by SQLite (no schemas).</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>plain name; blank = public. Ignored by SQLite, which has no schemas</t>
+          <t>plain name; blank = public. Ignored by SQLite</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1407,12 +1378,14 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Put in front of every generated table name, e.g. stg_ turns sales into stg_sales.</t>
+          <t>A prefix added to every table name.
+Example: if table_prefix='stg_' and table_name='orders', the physical table is 'stg_orders'. Useful for separating staging from production tables in the same schema.
+Blank = no prefix (default).</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>plain name fragment, letters/digits/underscore; blank = no prefix (default)</t>
+          <t>plain name fragment; blank = no prefix</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1434,7 +1407,9 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>How every primary key and the file_id are generated: a database counter (1, 2, 3...) or a UUID generated for each row.</t>
+          <t>How primary keys and file_id are generated.
+  'integer' → auto-incrementing numbers (1, 2, 3...) — simpler, default.
+  'uuid'    → random UUIDs per row — use when merging data from multiple sources where integer IDs would collide.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1459,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1516,7 +1491,8 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Logical table name for this block. The table created is &lt;table_prefix&gt;&lt;table_name&gt;.</t>
+          <t>The database table name for this block. The physical table becomes &lt;table_prefix&gt;&lt;table_name&gt;.
+Example: if your source has an 'Orders' tab, you might name it 'orders'. Two blocks on the same sheet need different names — e.g. 'card_payments' and 'cash_payments' for two sections on a 'Payments' tab.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1526,7 +1502,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>orders</t>
         </is>
       </c>
     </row>
@@ -1543,17 +1519,18 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Worksheet tab in the SOURCE workbook that this block sits on.</t>
+          <t>The exact tab name in the SOURCE workbook. Must match character for character — copy-paste it from the tab to avoid typos.
+Example: if the tab is called 'Order Level', type exactly 'Order Level'. Excel truncates long tab names (e.g. 'Growth Investments and Other De'), so copy the truncated name.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>must match the tab name character for character (Excel truncates long tab names)</t>
+          <t>exact tab name from the source file</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Order Level</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1547,15 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Shape of the block. Documentation for the reader - both are read cell by cell.</t>
+          <t>Describes the shape of the data block:
+  'table' = a header row (e.g. row 1) followed by data rows below it.
+  'key_value' = labels in one column, values in the next (like a settings block).
+Example: a list of orders with columns Date, Customer, Amount → 'table'. A summary block with 'Total Orders: 42' on one row → 'key_value'.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>table = header row + data rows | key_value = label column + value column</t>
+          <t>table | key_value</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1597,7 +1577,8 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Row that holds the printed headers. Never read as data; kept for the audit table.</t>
+          <t>The row number that contains column headers (e.g. 'Date', 'Customer', 'Amount'). Not read as data — only recorded in the audit log.
+Example: if row 1 has headers and data starts at row 2, set header_row=1. Leave blank for key_value layout.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1624,7 +1605,8 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>First row of real data.</t>
+          <t>The FIRST row of actual data (not the header, not a title row). Look at the row numbers in Excel.
+Example: if row 1 is headers and data starts at row 2, set data_start_row=2. If there is a title on rows 1–3, headers on row 4, and data from row 5, set data_start_row=5.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1651,7 +1633,9 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Last row of real data. Set it to fence off a totals row, notes, or a second block further down the sheet.</t>
+          <t>The LAST row of data. Set this when there are totals, notes, or another data block below.
+Example: data in rows 2–50, then a 'Grand Total' on row 51 → set data_end_row=50. If another block starts at row 55, fence this one off at row 50.
+Leave blank to read to the last non-empty row in the sheet.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1678,12 +1662,13 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Switch the block off without deleting the rows.</t>
+          <t>Y = this block is processed (table created, data loaded).
+N = completely skipped — use this to park a block you do not want right now without deleting the row.</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Y = generate the table and load it | N = ignore completely</t>
+          <t>Y | N</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1695,25 +1680,81 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>A human-readable description of what this table contains. Written as a COMMENT ON TABLE in PostgreSQL so BI tools and AI agents can discover meaning.
+Example: 'Order-level payout details from the Swiggy annexure'</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>any text</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Order-level payout details from the delivery platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>A business category tag. Prepended to the table comment as [domain].
+Example: 'finance', 'orders', 'inventory', 'hr'</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>any text</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>food_delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Free text; copied into the generated SQL as a comment.</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Free text for your own use. Copied into the generated SQL as a comment.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>any text</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>invoice lines, one row per invoice</t>
         </is>
@@ -1730,7 +1771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1787,7 +1828,8 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Which sheet_config block this column belongs to.</t>
+          <t>Which block (from sheet_config) this column belongs to.
+Example: if you defined a block called 'orders' in sheet_config, every column row for that block has table_name='orders'.</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1797,7 +1839,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>orders</t>
         </is>
       </c>
     </row>
@@ -1814,12 +1856,14 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Which Excel column of that block to read. Read by POSITION - re-check it whenever the supplier inserts a column.</t>
+          <t>Which Excel column letter to read FROM the source file. The parser reads by column position, NOT by header text.
+Example: if 'Order ID' is in column A → 'col:A'. If 'Amount' is in column D → 'col:D'. Wide sheets: column 30 = 'col:AD'.
+IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all source_ref values when that happens.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>col:&lt;letter&gt;, e.g. col:A, col:AM. No row numbers, no ranges, no formulas</t>
+          <t>col:&lt;letter&gt; (e.g. col:A, col:B, col:AM). No row numbers, no ranges</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1841,12 +1885,13 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>The header text as printed in the source file.</t>
+          <t>The header text as printed in the source file — purely for documentation. The parser never matches by header text; it always uses source_ref.
+Example: if column A has header 'Invoice No', put 'Invoice No' here. This shows up in the ER diagram and preview tooltips. If the supplier renames the header, the load still works — only source_ref matters.</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>any text; documentation only, a renamed header does not break the load</t>
+          <t>any text; documentation only</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1868,12 +1913,14 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Database column name to create.</t>
+          <t>The database column name to create. Must be unique within the table.
+Example: 'Invoice No' → 'invoice_no', 'Order Date' → 'order_date'.
+Reserved names (added automatically): file_id, sheet_name, source_row_num, &lt;table_name&gt;_id — do not use these.</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>lowercase letters/digits/underscore, unique within the table, max 63 chars; not file_id, sheet_name, source_row_num or &lt;table_name&gt;_id</t>
+          <t>lowercase letters/digits/underscore, unique within the table, max 63 chars</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1895,7 +1942,14 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>How the cell is converted. Pick it from the messiest value in the column, not the first one.</t>
+          <t>How the cell value is converted. Choose the type based on the MESSIEST value in the column, not just the first row.
+  text     → keeps the text, trims whitespace. Use for names, IDs, mixed content.
+  numeric  → extracts numbers: '₹1,234.50' → 1234.5, '18%' → 18.0
+  integer  → like numeric but truncated: '42.0' → 42
+  date     → converts to YYYY-MM-DD: '02-Aug-2026' → '2026-08-02'
+  timestamp → date + time: '2026-08-02 19:45'
+  boolean  → yes/true/1 → 1, no/false/0 → 0
+If ANY cell can hold '-', 'NA', or a note, use 'text' to avoid NULLs.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1922,17 +1976,21 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>May the cell be empty?</t>
+          <t>Can this column be empty in the source?
+  Y = empty cells are stored as NULL (most columns should use this).
+  N = NOT NULL — any row where this cell is empty is rejected and reported, not loaded.
+Example: 'order_id' should be N (every order must have an ID). 'discount' should be Y (not all orders have a discount).
+When in doubt, use Y — it is safer and you can tighten later.</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Y = allowed | N = NOT NULL, and a row with it empty is rejected and reported</t>
+          <t>Y | N</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -1949,7 +2007,8 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Create a plain index on this column (for lookups). NOT a primary key and it does not deduplicate.</t>
+          <t>Creates a non-unique INDEX on this column for faster lookups. This is NOT a primary key and does NOT deduplicate rows.
+Example: set Y on 'order_id' or 'invoice_no' — columns you will filter or join on. Set N on 'amount', 'description', etc.</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1959,61 +2018,211 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>column_order</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Intent of the cleaning. Documentation - the actual cleaning comes from data_type.</t>
+          <t>Controls the position of this column in the created table. Number them 1, 2, 3... in the order you want.
+Example: invoice_no=1, invoice_date=2, customer=3, amount=4.
+Gaps are fine (1, 5, 10); duplicates make the order arbitrary.</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>trim | money | percent | date | blank</t>
+          <t>whole number</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>trim</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>column_order</t>
+          <t>script</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Position of the column in the created table.</t>
+          <t>Transformations applied AFTER type casting on every cell value. Chain multiple with | (pipe).
+TEXT examples:
+  trim             '  hello  ' → 'hello'
+  uppercase        'hello' → 'HELLO'
+  lowercase        'HELLO' → 'hello'
+  titlecase        'hello world' → 'Hello World'
+  digits_only      'INV-001' → '001'
+  letters_only     'Order-123' → 'Order'
+  alphanum_only    'Order #123!' → 'Order123'
+  collapse_spaces  'hello    world' → 'hello world'
+  replace_newlines 'line1\nline2' → 'line1 line2'
+  remove_punctuation 'Hello, World!' → 'Hello World'
+  first_word       'John Smith' → 'John'
+  last_word        'John Smith' → 'Smith'
+  left_10 / right_10  first/last 10 characters
+  slug             'Hello World!' → 'hello-world'
+NUMERIC examples:
+  abs              -120.5 → 120.5
+  negate           100 → -100
+  round_2          3.14159 → 3.14
+  round_1          3.456 → 3.5
+  round_0          3.7 → 4.0
+  floor / ceil     3.9 → 3 / 3.1 → 4
+  pct_to_fraction  18.0 → 0.18
+  fraction_to_pct  0.18 → 18.0
+  clamp_0          -5 → 0 (negatives become 0)
+DATE examples:
+  date_only        '2026-08-02T19:45' → '2026-08-02'
+  year_month       '2026-08-02' → '2026-08'
+  year_only        '2026-08-02' → '2026'
+GUARD:
+  not_null         error if NULL
+  not_empty        error if NULL or empty string</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>whole number; gaps are fine, duplicates make the order arbitrary</t>
+          <t>chain with |, e.g. trim|uppercase</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>trim</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>What this column represents. Written as a COMMENT ON COLUMN in PostgreSQL so BI tools and AI agents can understand the schema.
+Example: 'Unique order identifier assigned by the platform'</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>any text</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Unique order identifier from the platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Unit of measurement for numeric columns. Appended to the column comment.
+Example: 'INR' for Indian Rupees, 'USD', 'percent', 'count', 'kg'</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>any text</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>null_default</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>What to store when a cell is empty, instead of NULL.
+Examples:
+  numeric/integer column: '0' → stores 0 instead of NULL
+  text column: 'N/A' or '' → stores that string instead of NULL
+  boolean column: '0' or 'false' → stores 0 instead of NULL
+Applied after type casting, so a cell with '-' that casts to NULL also gets the default. Leave blank to keep NULL (the default behavior).</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>any value appropriate for the data_type; blank = store NULL</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>references</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Declares a foreign-key relationship to another table's column. Shown as a dashed line in the ER diagram. Does NOT create a database constraint — it is for documentation and the diagram only.
+Example: if this column references the 'order_id' column in the 'orders' table, write 'orders.order_id'. The ER diagram will draw an arrow from this column to orders.order_id.</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>table_name.column_name (must reference an existing table and column)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>orders.order_id</t>
         </is>
       </c>
     </row>

--- a/examples/07_validation_errors/broken_config.xlsx
+++ b/examples/07_validation_errors/broken_config.xlsx
@@ -287,6 +287,28 @@
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
+        <t xml:space="preserve">row_filter (optional)
+Skip rows that don't match this condition.
+Use col:LETTER to reference a cell (same as source_ref), then an operator and a value.
+Operators:
+  =  !=  &gt;  &lt;  &gt;=  &lt;=        compare text or numbers
+  contains  not_contains     text search inside the cell
+  is_empty  is_not_empty     check for blank cells (no value needed)
+Examples:
+  col:A is_not_empty              skip blank rows
+  col:D &gt; 0                       only positive amounts
+  col:B = "Delivered"             only delivered orders
+  col:C != "Cancelled"            exclude cancelled
+  col:E contains "swiggy"         cell contains the word
+  col:D &gt; 100 AND col:F != "NA"   combine two conditions
+  col:A = "Active" OR col:A = "Pending"   either status
+Leave blank to load all rows (default).
+Allowed: col:LETTER op value [AND/OR ...]; blank = all rows
+Example: </t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
         <t>active (required)
 Y = this block is processed (table created, data loaded).
 N = completely skipped — use this to park a block you do not want right now without deleting the row.
@@ -294,7 +316,7 @@
 Example: Y</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>notes (optional)
 Free text for your own use. Copied into the generated SQL as a comment.
@@ -324,10 +346,30 @@
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <t>source_ref (required)
-Which Excel column letter to read FROM the source file. The parser reads by column position, NOT by header text.
-Example: if 'Order ID' is in column A → 'col:A'. If 'Amount' is in column D → 'col:D'. Wide sheets: column 30 = 'col:AD'.
-IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all source_ref values when that happens.
-Allowed: col:&lt;letter&gt; (e.g. col:A, col:B, col:AM). No row numbers, no ranges
+Where to get the value for this column. Four formats:
+1. Column reference: 'col:&lt;letter&gt;' — reads from the source file by position, NOT by header text. Example: col:A, col:D, col:AM.
+2. Constant value: 'const:&lt;value&gt;' — fills every row with a fixed value. Example: const:adarsh, const:100.
+3. Computed value: 'fn:&lt;name&gt;' — fills every row with a value computed at load time. Available functions:
+  fn:now       — current timestamp (timestamp, text)
+  fn:today     — current date (date, text)
+  fn:uuid      — random UUID per row (text)
+  fn:file_name — source file name (text)
+  fn:sequence  — counter 1,2,3... per table (integer, numeric, text)
+4. Expression: 'expr:&lt;expression&gt;' — computes a value from other columns, constants, functions and literals. Use {X} to reference Excel column X.
+  Operators: + - * / (numeric), &amp; (string concatenation)
+  Grouping: parentheses ( ) to override precedence
+  Unary minus: -{A} to negate a value
+  NULL handling: arithmetic with NULL -&gt; NULL (like SQL)
+  Examples:
+    expr:{D} + {E}             (sum two columns)
+    expr:({A} + {B}) * {C}     (grouped arithmetic)
+    expr:-{D}                  (negate a value)
+    expr:{A} &amp; " - " &amp; {C}    (concatenate with separator)
+    expr:{D} * 0.18            (calculate 18% tax)
+All results are cast to the column's data_type. 'script' and
+'null_default' apply after the expression result is cast.
+IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all col: and expr: source_ref values when that happens.
+Allowed: col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, or expr:&lt;expression&gt;
 Example: col:A</t>
       </text>
     </comment>
@@ -394,6 +436,21 @@
 Gaps are fine (1, 5, 10); duplicates make the order arbitrary.
 Allowed: whole number
 Example: 1</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">date_format (optional)
+Pin the date parsing to a specific format instead of auto-detecting.
+Without this, the parser tries multiple formats in order — which means '01/02/2026' could be January 2 or February 1 depending on which format matches first.
+Set this to eliminate ambiguity:
+  %d/%m/%Y   → DD/MM/YYYY (European/Indian: 01/02/2026 = Feb 1)
+  %m/%d/%Y   → MM/DD/YYYY (American: 01/02/2026 = Jan 2)
+  %Y-%m-%d   → YYYY-MM-DD (ISO)
+  %d-%b-%Y   → DD-Mon-YYYY (02-Aug-2026)
+Only applies to date and timestamp columns. Ignored for other types.
+Allowed: Python strptime format string; blank = auto-detect
+Example: </t>
       </text>
     </comment>
   </commentList>
@@ -801,7 +858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -812,6 +869,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -847,10 +905,15 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>row_filter</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>active</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -878,12 +941,12 @@
       <c r="E2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>the only correct block</t>
         </is>
@@ -911,12 +974,12 @@
       <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>table_name with a space</t>
         </is>
@@ -944,12 +1007,12 @@
       <c r="E4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>header_row sits inside the data</t>
         </is>
@@ -967,7 +1030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -978,6 +1041,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1019,6 +1083,11 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>column_order</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>date_format</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1652,109 +1721,146 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t>row_filter</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Skip rows that don't match this condition.
+Use col:LETTER to reference a cell (same as source_ref), then an operator and a value.
+Operators:
+  =  !=  &gt;  &lt;  &gt;=  &lt;=        compare text or numbers
+  contains  not_contains     text search inside the cell
+  is_empty  is_not_empty     check for blank cells (no value needed)
+Examples:
+  col:A is_not_empty              skip blank rows
+  col:D &gt; 0                       only positive amounts
+  col:B = "Delivered"             only delivered orders
+  col:C != "Cancelled"            exclude cancelled
+  col:E contains "swiggy"         cell contains the word
+  col:D &gt; 100 AND col:F != "NA"   combine two conditions
+  col:A = "Active" OR col:A = "Pending"   either status
+Leave blank to load all rows (default).</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>col:LETTER op value [AND/OR ...]; blank = all rows</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Y = this block is processed (table created, data loaded).
 N = completely skipped — use this to park a block you do not want right now without deleting the row.</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Y | N</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>A human-readable description of what this table contains. Written as a COMMENT ON TABLE in PostgreSQL so BI tools and AI agents can discover meaning.
 Example: 'Order-level payout details from the Swiggy annexure'</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>any text</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Order-level payout details from the delivery platform</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>A business category tag. Prepended to the table comment as [domain].
 Example: 'finance', 'orders', 'inventory', 'hr'</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>any text</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>food_delivery</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Free text for your own use. Copied into the generated SQL as a comment.</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>any text</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>invoice lines, one row per invoice</t>
         </is>
@@ -1771,7 +1877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1856,14 +1962,34 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Which Excel column letter to read FROM the source file. The parser reads by column position, NOT by header text.
-Example: if 'Order ID' is in column A → 'col:A'. If 'Amount' is in column D → 'col:D'. Wide sheets: column 30 = 'col:AD'.
-IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all source_ref values when that happens.</t>
+          <t>Where to get the value for this column. Four formats:
+1. Column reference: 'col:&lt;letter&gt;' — reads from the source file by position, NOT by header text. Example: col:A, col:D, col:AM.
+2. Constant value: 'const:&lt;value&gt;' — fills every row with a fixed value. Example: const:adarsh, const:100.
+3. Computed value: 'fn:&lt;name&gt;' — fills every row with a value computed at load time. Available functions:
+  fn:now       — current timestamp (timestamp, text)
+  fn:today     — current date (date, text)
+  fn:uuid      — random UUID per row (text)
+  fn:file_name — source file name (text)
+  fn:sequence  — counter 1,2,3... per table (integer, numeric, text)
+4. Expression: 'expr:&lt;expression&gt;' — computes a value from other columns, constants, functions and literals. Use {X} to reference Excel column X.
+  Operators: + - * / (numeric), &amp; (string concatenation)
+  Grouping: parentheses ( ) to override precedence
+  Unary minus: -{A} to negate a value
+  NULL handling: arithmetic with NULL -&gt; NULL (like SQL)
+  Examples:
+    expr:{D} + {E}             (sum two columns)
+    expr:({A} + {B}) * {C}     (grouped arithmetic)
+    expr:-{D}                  (negate a value)
+    expr:{A} &amp; " - " &amp; {C}    (concatenate with separator)
+    expr:{D} * 0.18            (calculate 18% tax)
+All results are cast to the column's data_type. 'script' and
+'null_default' apply after the expression result is cast.
+IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all col: and expr: source_ref values when that happens.</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>col:&lt;letter&gt; (e.g. col:A, col:B, col:AM). No row numbers, no ranges</t>
+          <t>col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, or expr:&lt;expression&gt;</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -2226,6 +2352,36 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>date_format</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Pin the date parsing to a specific format instead of auto-detecting.
+Without this, the parser tries multiple formats in order — which means '01/02/2026' could be January 2 or February 1 depending on which format matches first.
+Set this to eliminate ambiguity:
+  %d/%m/%Y   → DD/MM/YYYY (European/Indian: 01/02/2026 = Feb 1)
+  %m/%d/%Y   → MM/DD/YYYY (American: 01/02/2026 = Jan 2)
+  %Y-%m-%d   → YYYY-MM-DD (ISO)
+  %d-%b-%Y   → DD-Mon-YYYY (02-Aug-2026)
+Only applies to date and timestamp columns. Ignored for other types.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Python strptime format string; blank = auto-detect</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/07_validation_errors/broken_config.xlsx
+++ b/examples/07_validation_errors/broken_config.xlsx
@@ -779,7 +779,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>broken.db</t>
+          <t>excel_parser</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -809,6 +809,11 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>db_schema</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>broken</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/examples/07_validation_errors/broken_config.xlsx
+++ b/examples/07_validation_errors/broken_config.xlsx
@@ -366,10 +366,14 @@
     expr:-{D}                  (negate a value)
     expr:{A} &amp; " - " &amp; {C}    (concatenate with separator)
     expr:{D} * 0.18            (calculate 18% tax)
+5. Positional map: 'map:v1||v2||v3||...' — assigns a different value to each row by position. The first data row gets v1, the second gets v2, and so on. Use || (double pipe) to separate values.
+  Example: map:Name||Area||City||ID||GSTIN
+  Ideal for key_value blocks where the source has no label column.
+  If the map has fewer values than rows, extra rows get NULL.
 All results are cast to the column's data_type. 'script' and
 'null_default' apply after the expression result is cast.
 IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all col: and expr: source_ref values when that happens.
-Allowed: col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, or expr:&lt;expression&gt;
+Allowed: col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, expr:&lt;expression&gt;, or map:v1||v2||...
 Example: col:A</t>
       </text>
     </comment>
@@ -1987,6 +1991,10 @@
     expr:-{D}                  (negate a value)
     expr:{A} &amp; " - " &amp; {C}    (concatenate with separator)
     expr:{D} * 0.18            (calculate 18% tax)
+5. Positional map: 'map:v1||v2||v3||...' — assigns a different value to each row by position. The first data row gets v1, the second gets v2, and so on. Use || (double pipe) to separate values.
+  Example: map:Name||Area||City||ID||GSTIN
+  Ideal for key_value blocks where the source has no label column.
+  If the map has fewer values than rows, extra rows get NULL.
 All results are cast to the column's data_type. 'script' and
 'null_default' apply after the expression result is cast.
 IMPORTANT: if the supplier inserts a new column, every letter after it shifts. Re-check all col: and expr: source_ref values when that happens.</t>
@@ -1994,7 +2002,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, or expr:&lt;expression&gt;</t>
+          <t>col:&lt;letter&gt;, const:&lt;value&gt;, fn:&lt;name&gt;, expr:&lt;expression&gt;, or map:v1||v2||...</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
